--- a/docs/audit/inventory_business_import.xlsx
+++ b/docs/audit/inventory_business_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,11 @@
           <t>未来预测_2026-10</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>未来预测_2026-11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -507,6 +512,9 @@
       <c r="J2" t="n">
         <v>3200</v>
       </c>
+      <c r="K2" t="n">
+        <v>3200</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -547,6 +555,9 @@
       <c r="J3" t="n">
         <v>3200</v>
       </c>
+      <c r="K3" t="n">
+        <v>3200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,6 +598,9 @@
       <c r="J4" t="n">
         <v>2800</v>
       </c>
+      <c r="K4" t="n">
+        <v>2800</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -627,6 +641,9 @@
       <c r="J5" t="n">
         <v>1500</v>
       </c>
+      <c r="K5" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +684,9 @@
       <c r="J6" t="n">
         <v>1300</v>
       </c>
+      <c r="K6" t="n">
+        <v>1300</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -707,6 +727,9 @@
       <c r="J7" t="n">
         <v>900</v>
       </c>
+      <c r="K7" t="n">
+        <v>900</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -747,6 +770,9 @@
       <c r="J8" t="n">
         <v>1200</v>
       </c>
+      <c r="K8" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -787,6 +813,9 @@
       <c r="J9" t="n">
         <v>2200</v>
       </c>
+      <c r="K9" t="n">
+        <v>2200</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -825,6 +854,9 @@
         <v>900</v>
       </c>
       <c r="J10" t="n">
+        <v>900</v>
+      </c>
+      <c r="K10" t="n">
         <v>900</v>
       </c>
     </row>
